--- a/yolo-seg__ANN/根管填充物像素長度_已配對_mask幾何_長邊正規化.xlsx
+++ b/yolo-seg__ANN/根管填充物像素長度_已配對_mask幾何_長邊正規化.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -820,7 +820,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>mask幾何_長邊正規化_seed4</t>
+          <t>mask幾何_長邊正規化</t>
         </is>
       </c>
       <c r="G68" t="n">
